--- a/artfynd/A 57513-2025 artfynd.xlsx
+++ b/artfynd/A 57513-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68041140</v>
+        <v>134796619</v>
       </c>
       <c r="B7" t="n">
-        <v>104628</v>
+        <v>99101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1285,21 +1285,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ope 2:2, Främmerbodarna /430 m S/, Jmt</t>
+          <t>Ope, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489810</v>
+        <v>489863</v>
       </c>
       <c r="R7" t="n">
-        <v>7001301</v>
+        <v>7001335</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,17 +1321,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 buske. I övre delen av ytterslänt till asfalterad väg, tidigare flygets väg. Del av fuktstråk mynnar här.</t>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,24 +1347,135 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Ytterslänt asfaltväg, fuktstråk</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Arne Holgersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>68041140</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ope 2:2, Främmerbodarna /430 m S/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489810</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7001301</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 buske. I övre delen av ytterslänt till asfalterad väg, tidigare flygets väg. Del av fuktstråk mynnar här.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Ytterslänt asfaltväg, fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Lars-Åke Bäckström, Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
